--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130177144</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130177140</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>130177139</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130177152</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,45 +1570,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130177162</v>
+        <v>130177147</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604719</v>
+        <v>604710</v>
       </c>
       <c r="R11" t="n">
-        <v>6674909</v>
+        <v>6674877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130177147</v>
+        <v>130177142</v>
       </c>
       <c r="B12" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,7 +1701,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1706,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604710</v>
+        <v>604689</v>
       </c>
       <c r="R12" t="n">
-        <v>6674877</v>
+        <v>6674748</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,49 +1772,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130177142</v>
+        <v>130177162</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604689</v>
+        <v>604719</v>
       </c>
       <c r="R13" t="n">
-        <v>6674748</v>
+        <v>6674909</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1872,7 +1872,7 @@
         <v>130177156</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130177163</v>
+        <v>130177144</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604712</v>
+        <v>604701</v>
       </c>
       <c r="R2" t="n">
-        <v>6674910</v>
+        <v>6674743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,49 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130177144</v>
+        <v>130177163</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604701</v>
+        <v>604712</v>
       </c>
       <c r="R3" t="n">
-        <v>6674743</v>
+        <v>6674910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,7 +877,7 @@
         <v>130177133</v>
       </c>
       <c r="B4" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130177140</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>130177164</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>130177161</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>130177130</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>130177139</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130177152</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>130177147</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,49 +1671,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130177142</v>
+        <v>130177162</v>
       </c>
       <c r="B12" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604689</v>
+        <v>604719</v>
       </c>
       <c r="R12" t="n">
-        <v>6674748</v>
+        <v>6674909</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,45 +1768,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130177162</v>
+        <v>130177142</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604719</v>
+        <v>604689</v>
       </c>
       <c r="R13" t="n">
-        <v>6674909</v>
+        <v>6674748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1872,7 +1872,7 @@
         <v>130177156</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130177163</v>
+        <v>130177144</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604712</v>
+        <v>604701</v>
       </c>
       <c r="R2" t="n">
-        <v>6674910</v>
+        <v>6674743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,49 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130177144</v>
+        <v>130177163</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604701</v>
+        <v>604712</v>
       </c>
       <c r="R3" t="n">
-        <v>6674743</v>
+        <v>6674910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177164</v>
+        <v>130177161</v>
       </c>
       <c r="B6" t="n">
         <v>79180</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604725</v>
+        <v>604717</v>
       </c>
       <c r="R6" t="n">
-        <v>6674909</v>
+        <v>6674900</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177161</v>
+        <v>130177164</v>
       </c>
       <c r="B7" t="n">
         <v>79180</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604717</v>
+        <v>604725</v>
       </c>
       <c r="R7" t="n">
-        <v>6674900</v>
+        <v>6674909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130177144</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130177163</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130177140</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177161</v>
+        <v>130177164</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604717</v>
+        <v>604725</v>
       </c>
       <c r="R6" t="n">
-        <v>6674900</v>
+        <v>6674909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177164</v>
+        <v>130177161</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604725</v>
+        <v>604717</v>
       </c>
       <c r="R7" t="n">
-        <v>6674909</v>
+        <v>6674900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1371,7 @@
         <v>130177139</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130177152</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>130177162</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130177147</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130177142</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>130177156</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>130382906</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130382904</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>130382905</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130177144</v>
+        <v>130177163</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604701</v>
+        <v>604712</v>
       </c>
       <c r="R2" t="n">
-        <v>6674743</v>
+        <v>6674910</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130177163</v>
+        <v>130177144</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604712</v>
+        <v>604701</v>
       </c>
       <c r="R3" t="n">
-        <v>6674910</v>
+        <v>6674743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,7 +877,7 @@
         <v>130177133</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130177140</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177164</v>
+        <v>130177161</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604725</v>
+        <v>604717</v>
       </c>
       <c r="R6" t="n">
-        <v>6674909</v>
+        <v>6674900</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177161</v>
+        <v>130177164</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604717</v>
+        <v>604725</v>
       </c>
       <c r="R7" t="n">
-        <v>6674900</v>
+        <v>6674909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1269,7 @@
         <v>130177130</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>130177139</v>
       </c>
       <c r="B9" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130177152</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>130177162</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130177147</v>
       </c>
       <c r="B12" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130177142</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>130177156</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>130382906</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130382904</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>130382905</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>130422383</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130177144</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130177140</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177161</v>
+        <v>130177164</v>
       </c>
       <c r="B6" t="n">
         <v>79209</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604717</v>
+        <v>604725</v>
       </c>
       <c r="R6" t="n">
-        <v>6674900</v>
+        <v>6674909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177164</v>
+        <v>130177161</v>
       </c>
       <c r="B7" t="n">
         <v>79209</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604725</v>
+        <v>604717</v>
       </c>
       <c r="R7" t="n">
-        <v>6674909</v>
+        <v>6674900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130177139</v>
+        <v>130177152</v>
       </c>
       <c r="B9" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604717</v>
+        <v>604677</v>
       </c>
       <c r="R9" t="n">
-        <v>6674880</v>
+        <v>6674882</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130177152</v>
+        <v>130177139</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604677</v>
+        <v>604717</v>
       </c>
       <c r="R10" t="n">
-        <v>6674882</v>
+        <v>6674880</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
         <v>130177147</v>
       </c>
       <c r="B12" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130177142</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>130177156</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130177163</v>
+        <v>130177144</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604712</v>
+        <v>604701</v>
       </c>
       <c r="R2" t="n">
-        <v>6674910</v>
+        <v>6674743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,49 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130177144</v>
+        <v>130177163</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604701</v>
+        <v>604712</v>
       </c>
       <c r="R3" t="n">
-        <v>6674743</v>
+        <v>6674910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -974,7 +974,7 @@
         <v>130177140</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130177152</v>
+        <v>130177139</v>
       </c>
       <c r="B9" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604677</v>
+        <v>604717</v>
       </c>
       <c r="R9" t="n">
-        <v>6674882</v>
+        <v>6674880</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130177139</v>
+        <v>130177152</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604717</v>
+        <v>604677</v>
       </c>
       <c r="R10" t="n">
-        <v>6674880</v>
+        <v>6674882</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1670,7 @@
         <v>130177147</v>
       </c>
       <c r="B12" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130177142</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>130177156</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130177144</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130177163</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130177133</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130177140</v>
       </c>
       <c r="B5" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>130177164</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>130177161</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>130177130</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>130177139</v>
       </c>
       <c r="B9" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>130177152</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>130177162</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>130177147</v>
       </c>
       <c r="B12" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>130177142</v>
       </c>
       <c r="B13" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>130177156</v>
       </c>
       <c r="B14" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>130382906</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130382904</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>130382905</v>
       </c>
       <c r="B17" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>130422383</v>
       </c>
       <c r="B18" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>130382906</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130382904</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>130382905</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>130422383</v>
       </c>
       <c r="B18" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>130382906</v>
       </c>
       <c r="B15" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130382904</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>130382905</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>130422383</v>
       </c>
       <c r="B18" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>130382906</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>130382904</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>130382905</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>130422383</v>
       </c>
       <c r="B18" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -1966,7 +1966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130382906</v>
+        <v>130382904</v>
       </c>
       <c r="B15" t="n">
         <v>79221</v>
@@ -1995,19 +1995,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604713</v>
+        <v>604692</v>
       </c>
       <c r="R15" t="n">
-        <v>6674908</v>
+        <v>6674779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,7 +2045,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2067,7 +2063,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130382904</v>
+        <v>130382906</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2096,16 +2092,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604692</v>
+        <v>604713</v>
       </c>
       <c r="R16" t="n">
-        <v>6674779</v>
+        <v>6674908</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,6 +2145,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -1966,7 +1966,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130382904</v>
+        <v>130382906</v>
       </c>
       <c r="B15" t="n">
         <v>79221</v>
@@ -1995,16 +1995,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604692</v>
+        <v>604713</v>
       </c>
       <c r="R15" t="n">
-        <v>6674779</v>
+        <v>6674908</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,6 +2048,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2067,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130382906</v>
+        <v>130382904</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2092,19 +2096,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604713</v>
+        <v>604692</v>
       </c>
       <c r="R16" t="n">
-        <v>6674908</v>
+        <v>6674779</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2146,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -2269,7 +2269,7 @@
         <v>130422383</v>
       </c>
       <c r="B18" t="n">
-        <v>57861</v>
+        <v>57875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130177144</v>
+        <v>130177161</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604701</v>
+        <v>604717</v>
       </c>
       <c r="R2" t="n">
-        <v>6674743</v>
+        <v>6674900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130177163</v>
+        <v>130177162</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604712</v>
+        <v>604719</v>
       </c>
       <c r="R3" t="n">
-        <v>6674910</v>
+        <v>6674909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130177133</v>
+        <v>130177163</v>
       </c>
       <c r="B4" t="n">
-        <v>58226</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604675</v>
+        <v>604712</v>
       </c>
       <c r="R4" t="n">
-        <v>6674768</v>
+        <v>6674910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130177140</v>
+        <v>130177164</v>
       </c>
       <c r="B5" t="n">
-        <v>98953</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,38 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604743</v>
+        <v>604725</v>
       </c>
       <c r="R5" t="n">
-        <v>6674927</v>
+        <v>6674909</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130177164</v>
+        <v>130382904</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1103,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Intill Nordansjö naturreservat, Upl</t>
+          <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604725</v>
+        <v>604692</v>
       </c>
       <c r="R6" t="n">
-        <v>6674909</v>
+        <v>6674779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1137,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1169,14 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130177161</v>
+        <v>130382905</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1200,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Intill Nordansjö naturreservat, Upl</t>
+          <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604717</v>
+        <v>604669</v>
       </c>
       <c r="R7" t="n">
-        <v>6674900</v>
+        <v>6674793</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1234,12 +1225,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1266,45 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130177130</v>
+        <v>130382906</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Intill Nordansjö naturreservat, Upl</t>
+          <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604700</v>
+        <v>604713</v>
       </c>
       <c r="R8" t="n">
-        <v>6674844</v>
+        <v>6674908</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1331,17 +1330,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1350,6 +1344,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1368,49 +1363,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130177139</v>
+        <v>130177130</v>
       </c>
       <c r="B9" t="n">
-        <v>98953</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604717</v>
+        <v>604700</v>
       </c>
       <c r="R9" t="n">
-        <v>6674880</v>
+        <v>6674844</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,6 +1434,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,49 +1465,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130177152</v>
+        <v>130422383</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intill Nordansjö naturreservat, Upl</t>
+          <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604677</v>
+        <v>604670</v>
       </c>
       <c r="R10" t="n">
-        <v>6674882</v>
+        <v>6674770</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,12 +1530,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1570,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130177162</v>
+        <v>130177133</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604719</v>
+        <v>604675</v>
       </c>
       <c r="R11" t="n">
-        <v>6674909</v>
+        <v>6674768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130177147</v>
+        <v>130177138</v>
       </c>
       <c r="B12" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1697,7 +1689,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1706,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604710</v>
+        <v>604784</v>
       </c>
       <c r="R12" t="n">
-        <v>6674877</v>
+        <v>6674931</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130177142</v>
+        <v>130177139</v>
       </c>
       <c r="B13" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,7 +1790,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1807,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604689</v>
+        <v>604717</v>
       </c>
       <c r="R13" t="n">
-        <v>6674748</v>
+        <v>6674880</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,10 +1861,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130177156</v>
+        <v>130177140</v>
       </c>
       <c r="B14" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1897,17 +1889,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604699</v>
+        <v>604743</v>
       </c>
       <c r="R14" t="n">
-        <v>6674728</v>
+        <v>6674927</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,48 +1962,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130382906</v>
+        <v>130177142</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nordansjö naturreservat, Upl</t>
+          <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604713</v>
+        <v>604689</v>
       </c>
       <c r="R15" t="n">
-        <v>6674908</v>
+        <v>6674748</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2034,12 +2031,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,7 +2045,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2067,45 +2063,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130382904</v>
+        <v>130177144</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nordansjö naturreservat, Upl</t>
+          <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604692</v>
+        <v>604701</v>
       </c>
       <c r="R16" t="n">
-        <v>6674779</v>
+        <v>6674743</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2146,6 +2146,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2164,45 +2165,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130382905</v>
+        <v>130177147</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nordansjö naturreservat, Upl</t>
+          <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604669</v>
+        <v>604710</v>
       </c>
       <c r="R17" t="n">
-        <v>6674793</v>
+        <v>6674877</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2229,17 +2234,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2266,45 +2266,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130422383</v>
+        <v>130177151</v>
       </c>
       <c r="B18" t="n">
-        <v>57875</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nordansjö naturreservat, Upl</t>
+          <t>Intill Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604670</v>
+        <v>604783</v>
       </c>
       <c r="R18" t="n">
-        <v>6674770</v>
+        <v>6674916</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2331,12 +2335,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2360,6 +2364,398 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130177152</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Intill Nordansjö naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>604677</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6674882</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130177155</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Intill Nordansjö naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>604783</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6674860</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130177156</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Intill Nordansjö naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>604699</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6674728</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130177132</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Intill Nordansjö naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>604721</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6674725</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54352-2025 artfynd.xlsx
+++ b/artfynd/A 54352-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177161</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177162</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177163</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177164</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382904</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382905</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382906</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177130</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130422383</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1656,6 +1706,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177133</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177138</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1858,6 +1918,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177139</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177140</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177142</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177144</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2263,6 +2343,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177147</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2364,6 +2449,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177151</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2465,6 +2555,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177152</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2562,6 +2657,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177155</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2659,6 +2759,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177156</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2756,8 +2861,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>